--- a/outputs/daily/hr_rankings_2026-08-09.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-09.xlsx
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -831,7 +831,7 @@
         <v>62.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -841,39 +841,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1059,24 +1055,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1094,12 +1090,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1108,7 +1104,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.5</v>
+        <v>59.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1122,14 +1118,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.3</v>
+        <v>40.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R3" t="n">
         <v>62.1</v>
@@ -1141,7 +1137,7 @@
         <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>72.2</v>
+        <v>51.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1193,12 +1189,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1213,107 +1209,107 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.5329</t>
+          <t>100.7812</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4627</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3309</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>55.07</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1696</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1359,24 +1355,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1394,12 +1390,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1408,7 +1404,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.2</v>
+        <v>57.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1422,62 +1418,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
         <v>62.1</v>
       </c>
       <c r="S4" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>33.9</v>
+        <v>72.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1497,127 +1489,127 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.6508</t>
+          <t>100.5329</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4627</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3309</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2075</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -1663,24 +1655,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1693,17 +1685,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1712,7 +1704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1726,62 +1718,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>40.5</v>
+        <v>51.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R5" t="n">
         <v>62.1</v>
       </c>
       <c r="S5" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1801,12 +1789,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1821,107 +1809,107 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.7812</t>
+          <t>104.2616</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.4593</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>75.51</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.07</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -1967,24 +1955,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1997,17 +1985,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2016,7 +2004,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2030,26 +2018,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.8</v>
+        <v>42.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R6" t="n">
         <v>62.1</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>50.8</v>
+        <v>33.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -2063,7 +2051,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2101,127 +2089,127 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.2616</t>
+          <t>101.6508</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4593</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>43.04</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.2075</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -2267,24 +2255,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2297,17 +2285,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2316,7 +2304,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>55.4</v>
+        <v>53.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2330,62 +2318,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>33.6</v>
+        <v>50.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
         <v>62.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2405,12 +2389,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2420,112 +2404,112 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.33</t>
+          <t>101.8619</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3967</t>
+          <t>0.4502</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.2002</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3018</t>
+          <t>0.3368</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1812</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2571,24 +2555,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2601,17 +2585,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2620,7 +2604,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.9</v>
+        <v>53.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2634,26 +2618,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50.3</v>
+        <v>31.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R8" t="n">
         <v>62.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>26.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2667,7 +2651,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2710,122 +2694,122 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/29, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.8619</t>
+          <t>100.0639</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4502</t>
+          <t>0.4404</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2002</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3368</t>
+          <t>0.3466</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2871,24 +2855,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2901,17 +2885,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2920,7 +2904,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.9</v>
+        <v>52</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2934,62 +2918,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>31.1</v>
+        <v>45.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
         <v>62.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>26.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3014,122 +2994,122 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.0639</t>
+          <t>101.3479</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4404</t>
+          <t>0.4376</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3466</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>24.76</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -3175,12 +3155,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3205,7 +3185,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3224,7 +3204,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.5</v>
+        <v>51.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3238,11 +3218,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>42.2</v>
+        <v>33.6</v>
       </c>
       <c r="Q10" t="n">
         <v>62.7</v>
@@ -3251,49 +3231,45 @@
         <v>62.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>81.7</v>
+        <v>0.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3313,27 +3289,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3343,67 +3319,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5346</t>
+          <t>99.33</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.3967</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1812</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3479,24 +3455,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -3514,12 +3490,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3528,7 +3504,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>50.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3542,14 +3518,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>45.1</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R11" t="n">
         <v>62.1</v>
@@ -3561,7 +3537,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>13.3</v>
+        <v>61.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3613,127 +3589,127 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>85.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.3479</t>
+          <t>97.1381</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4376</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1225</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -3828,7 +3804,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3842,7 +3818,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3855,7 +3831,7 @@
         <v>62.1</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
@@ -3865,39 +3841,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4083,24 +4055,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -4113,17 +4085,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4132,7 +4104,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4146,62 +4118,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R13" t="n">
         <v>62.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>61.4</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4221,7 +4189,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -4231,117 +4199,117 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.1381</t>
+          <t>98.1545</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1225</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.3022</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -4387,24 +4355,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -4417,17 +4385,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4436,7 +4404,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4450,26 +4418,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>17.5</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R14" t="n">
         <v>62.1</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>20.9</v>
+        <v>17.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4483,7 +4451,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4521,12 +4489,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4536,112 +4504,112 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>36.88</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.1545</t>
+          <t>99.4273</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.4244</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3022</t>
+          <t>0.3127</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.1533</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -4987,12 +4955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>664774</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5017,7 +4985,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5036,7 +5004,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>45.9</v>
+        <v>44.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5050,11 +5018,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>28.6</v>
+        <v>13.9</v>
       </c>
       <c r="Q16" t="n">
         <v>62.7</v>
@@ -5063,49 +5031,45 @@
         <v>62.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>17.7</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5125,12 +5089,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -5140,12 +5104,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -5155,67 +5119,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.88</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>86.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.4273</t>
+          <t>97.8228</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4244</t>
+          <t>0.2958</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1013</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3127</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -6586,7 +6550,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6600,7 +6564,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6613,7 +6577,7 @@
         <v>62.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6623,39 +6587,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6841,24 +6801,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -6876,12 +6836,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -6890,7 +6850,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.5</v>
+        <v>59.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6904,14 +6864,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.3</v>
+        <v>40.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R3" t="n">
         <v>62.1</v>
@@ -6923,7 +6883,7 @@
         <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>72.2</v>
+        <v>51.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -6975,12 +6935,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -6995,107 +6955,107 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.5329</t>
+          <t>100.7812</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4627</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3309</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>55.07</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1696</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -7141,24 +7101,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7176,12 +7136,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -7190,7 +7150,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.2</v>
+        <v>57.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7204,62 +7164,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
         <v>62.1</v>
       </c>
       <c r="S4" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>33.9</v>
+        <v>72.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7279,127 +7235,127 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.6508</t>
+          <t>100.5329</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4627</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3309</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2075</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -7445,24 +7401,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7475,17 +7431,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7494,7 +7450,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7508,62 +7464,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>40.5</v>
+        <v>51.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R5" t="n">
         <v>62.1</v>
       </c>
       <c r="S5" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7583,12 +7535,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -7603,107 +7555,107 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.7812</t>
+          <t>104.2616</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.4593</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>75.51</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.07</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -7749,24 +7701,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7779,17 +7731,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7798,7 +7750,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7812,26 +7764,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.8</v>
+        <v>42.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R6" t="n">
         <v>62.1</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>50.8</v>
+        <v>33.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7845,7 +7797,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7883,127 +7835,127 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.2616</t>
+          <t>101.6508</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4593</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>43.04</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.2075</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -8049,24 +8001,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -8079,17 +8031,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -8098,7 +8050,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>55.4</v>
+        <v>53.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8112,62 +8064,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>33.6</v>
+        <v>50.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
         <v>62.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8187,12 +8135,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -8202,112 +8150,112 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.33</t>
+          <t>101.8619</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3967</t>
+          <t>0.4502</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.2002</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3018</t>
+          <t>0.3368</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1812</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -8353,24 +8301,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -8383,17 +8331,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -8402,7 +8350,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.9</v>
+        <v>53.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8416,26 +8364,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50.3</v>
+        <v>31.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R8" t="n">
         <v>62.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>26.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -8449,7 +8397,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -8492,122 +8440,122 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/29, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.8619</t>
+          <t>100.0639</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4502</t>
+          <t>0.4404</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2002</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3368</t>
+          <t>0.3466</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -8653,24 +8601,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -8683,17 +8631,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8702,7 +8650,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.9</v>
+        <v>52</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8716,62 +8664,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>31.1</v>
+        <v>45.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
         <v>62.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>26.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8796,122 +8740,122 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.0639</t>
+          <t>101.3479</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4404</t>
+          <t>0.4376</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3466</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>24.76</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -8957,12 +8901,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8987,7 +8931,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9006,7 +8950,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.5</v>
+        <v>51.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9020,11 +8964,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>42.2</v>
+        <v>33.6</v>
       </c>
       <c r="Q10" t="n">
         <v>62.7</v>
@@ -9033,49 +8977,45 @@
         <v>62.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>81.7</v>
+        <v>0.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9095,27 +9035,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -9125,67 +9065,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5346</t>
+          <t>99.33</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.3967</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1812</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -9261,24 +9201,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -9296,12 +9236,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9310,7 +9250,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>50.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9324,14 +9264,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>45.1</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R11" t="n">
         <v>62.1</v>
@@ -9343,7 +9283,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>13.3</v>
+        <v>61.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -9395,127 +9335,127 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>85.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.3479</t>
+          <t>97.1381</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4376</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1225</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -9610,7 +9550,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9624,7 +9564,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -9637,7 +9577,7 @@
         <v>62.1</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
@@ -9647,39 +9587,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9865,24 +9801,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -9895,17 +9831,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9914,7 +9850,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9928,62 +9864,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R13" t="n">
         <v>62.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>61.4</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10003,7 +9935,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -10013,117 +9945,117 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.1381</t>
+          <t>98.1545</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1225</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.3022</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -10169,24 +10101,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -10199,17 +10131,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10218,7 +10150,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10232,26 +10164,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>17.5</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R14" t="n">
         <v>62.1</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>20.9</v>
+        <v>17.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -10265,7 +10197,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -10303,12 +10235,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -10318,112 +10250,112 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>36.88</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.1545</t>
+          <t>99.4273</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.4244</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3022</t>
+          <t>0.3127</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.1533</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -10769,12 +10701,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>664774</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10799,7 +10731,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10818,7 +10750,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>45.9</v>
+        <v>44.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10832,11 +10764,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>28.6</v>
+        <v>13.9</v>
       </c>
       <c r="Q16" t="n">
         <v>62.7</v>
@@ -10845,49 +10777,45 @@
         <v>62.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>17.7</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10907,12 +10835,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10922,12 +10850,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10937,67 +10865,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.88</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>86.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.4273</t>
+          <t>97.8228</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4244</t>
+          <t>0.2958</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1013</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3127</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-09.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-09.xlsx
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.6</v>
+        <v>57.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.5</v>
+        <v>55.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>53.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.4</v>
+        <v>53.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.9</v>
+        <v>51.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.5</v>
+        <v>51.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.7</v>
+        <v>49.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.2</v>
+        <v>47.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.7</v>
+        <v>44.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>46.2</v>
+        <v>44.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.3</v>
+        <v>42.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>42.3</v>
+        <v>40.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>40.2</v>
+        <v>38.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.3</v>
+        <v>35.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.6</v>
+        <v>57.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.5</v>
+        <v>55.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>53.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.4</v>
+        <v>53.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.9</v>
+        <v>51.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.5</v>
+        <v>51.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.7</v>
+        <v>49.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.2</v>
+        <v>47.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.7</v>
+        <v>44.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>46.2</v>
+        <v>44.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.3</v>
+        <v>42.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -11050,7 +11050,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>42.3</v>
+        <v>40.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>40.2</v>
+        <v>38.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -11650,7 +11650,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.3</v>
+        <v>35.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
